--- a/INSTANCES/instances_xlsx/A_MTN_8/405FL_15A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/405FL_15A_4.xlsx
@@ -12813,7 +12813,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -12881,7 +12881,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12898,7 +12898,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -12949,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -12983,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -13000,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
